--- a/public/exportTemplates/types.xlsx
+++ b/public/exportTemplates/types.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempShare\KYVL_CC_Plus\Export samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1F8A3C-E2E3-432E-A3F5-522459431F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBE3406-FF58-4A93-B750-40B72B760D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="705" yWindow="4110" windowWidth="24645" windowHeight="14385" xr2:uid="{B9EF07C2-5FC7-4CE7-9673-D90604365E4E}"/>
+    <workbookView xWindow="20520" yWindow="2580" windowWidth="15750" windowHeight="15795" xr2:uid="{B9EF07C2-5FC7-4CE7-9673-D90604365E4E}"/>
   </bookViews>
   <sheets>
     <sheet name="HowToImport" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t xml:space="preserve"> * Any Import rows without an ID in column A will be ignored.</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t xml:space="preserve"> * The Institution Types tab represents a starting place for updating or importing settings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * Type ID:1 is reserved for system use to denote intitutions that are "(Not classified)".</t>
   </si>
 </sst>
 </file>
@@ -530,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61435222-92B6-49F6-86EB-B1E85EE40C8D}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -564,7 +567,7 @@
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -576,7 +579,7 @@
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -588,7 +591,7 @@
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -600,7 +603,7 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -612,7 +615,7 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -622,73 +625,86 @@
       <c r="G7" s="5"/>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="9"/>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="8">
-    <mergeCell ref="A7:H7"/>
+  <mergeCells count="9">
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
